--- a/Team-Data/2014-15/12-4-2014-15.xlsx
+++ b/Team-Data/2014-15/12-4-2014-15.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,7 +806,7 @@
         <v>2.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AE2" t="n">
         <v>11</v>
@@ -754,7 +821,7 @@
         <v>6</v>
       </c>
       <c r="AI2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AJ2" t="n">
         <v>25</v>
@@ -793,7 +860,7 @@
         <v>3</v>
       </c>
       <c r="AV2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AW2" t="n">
         <v>5</v>
@@ -802,7 +869,7 @@
         <v>9</v>
       </c>
       <c r="AY2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AZ2" t="n">
         <v>5</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>12-4-2014-15</t>
+          <t>2014-12-04</t>
         </is>
       </c>
     </row>
@@ -921,7 +988,7 @@
         <v>-3.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AE3" t="n">
         <v>22</v>
@@ -945,7 +1012,7 @@
         <v>11</v>
       </c>
       <c r="AL3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AM3" t="n">
         <v>11</v>
@@ -954,7 +1021,7 @@
         <v>27</v>
       </c>
       <c r="AO3" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AP3" t="n">
         <v>29</v>
@@ -978,7 +1045,7 @@
         <v>15</v>
       </c>
       <c r="AW3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AX3" t="n">
         <v>25</v>
@@ -987,7 +1054,7 @@
         <v>24</v>
       </c>
       <c r="AZ3" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="BA3" t="n">
         <v>30</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>12-4-2014-15</t>
+          <t>2014-12-04</t>
         </is>
       </c>
     </row>
@@ -1103,16 +1170,16 @@
         <v>-0.9</v>
       </c>
       <c r="AD4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AE4" t="n">
         <v>18</v>
       </c>
       <c r="AF4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AG4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AH4" t="n">
         <v>1</v>
@@ -1121,10 +1188,10 @@
         <v>18</v>
       </c>
       <c r="AJ4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AK4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AL4" t="n">
         <v>19</v>
@@ -1133,25 +1200,25 @@
         <v>20</v>
       </c>
       <c r="AN4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AO4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AP4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AQ4" t="n">
         <v>6</v>
       </c>
       <c r="AR4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AS4" t="n">
         <v>10</v>
       </c>
       <c r="AT4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AU4" t="n">
         <v>24</v>
@@ -1160,7 +1227,7 @@
         <v>17</v>
       </c>
       <c r="AW4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AX4" t="n">
         <v>21</v>
@@ -1169,10 +1236,10 @@
         <v>12</v>
       </c>
       <c r="AZ4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BB4" t="n">
         <v>19</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>12-4-2014-15</t>
+          <t>2014-12-04</t>
         </is>
       </c>
     </row>
@@ -1312,7 +1379,7 @@
         <v>27</v>
       </c>
       <c r="AM5" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AN5" t="n">
         <v>29</v>
@@ -1321,25 +1388,25 @@
         <v>24</v>
       </c>
       <c r="AP5" t="n">
+        <v>23</v>
+      </c>
+      <c r="AQ5" t="n">
         <v>22</v>
       </c>
-      <c r="AQ5" t="n">
-        <v>23</v>
-      </c>
       <c r="AR5" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AS5" t="n">
         <v>14</v>
       </c>
       <c r="AT5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AU5" t="n">
         <v>15</v>
       </c>
       <c r="AV5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AW5" t="n">
         <v>29</v>
@@ -1351,13 +1418,13 @@
         <v>8</v>
       </c>
       <c r="AZ5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BA5" t="n">
         <v>13</v>
       </c>
       <c r="BB5" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BC5" t="n">
         <v>28</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>12-4-2014-15</t>
+          <t>2014-12-04</t>
         </is>
       </c>
     </row>
@@ -1470,7 +1537,7 @@
         <v>4</v>
       </c>
       <c r="AE6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF6" t="n">
         <v>11</v>
@@ -1491,25 +1558,25 @@
         <v>13</v>
       </c>
       <c r="AL6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AM6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AN6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AO6" t="n">
         <v>4</v>
       </c>
       <c r="AP6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AQ6" t="n">
         <v>16</v>
       </c>
       <c r="AR6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AS6" t="n">
         <v>6</v>
@@ -1533,10 +1600,10 @@
         <v>11</v>
       </c>
       <c r="AZ6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BB6" t="n">
         <v>12</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>12-4-2014-15</t>
+          <t>2014-12-04</t>
         </is>
       </c>
     </row>
@@ -1571,157 +1638,157 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F7" t="n">
         <v>7</v>
       </c>
       <c r="G7" t="n">
-        <v>0.588</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="H7" t="n">
         <v>48.3</v>
       </c>
       <c r="I7" t="n">
-        <v>37.1</v>
+        <v>37.4</v>
       </c>
       <c r="J7" t="n">
-        <v>80.3</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="K7" t="n">
-        <v>0.462</v>
+        <v>0.463</v>
       </c>
       <c r="L7" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="M7" t="n">
-        <v>21.2</v>
+        <v>21.4</v>
       </c>
       <c r="N7" t="n">
-        <v>0.357</v>
+        <v>0.362</v>
       </c>
       <c r="O7" t="n">
         <v>21.1</v>
       </c>
       <c r="P7" t="n">
-        <v>27.3</v>
+        <v>27.4</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.774</v>
+        <v>0.772</v>
       </c>
       <c r="R7" t="n">
-        <v>9.9</v>
+        <v>10.2</v>
       </c>
       <c r="S7" t="n">
-        <v>30.6</v>
+        <v>30.9</v>
       </c>
       <c r="T7" t="n">
-        <v>40.6</v>
+        <v>41.1</v>
       </c>
       <c r="U7" t="n">
-        <v>21.6</v>
+        <v>21.8</v>
       </c>
       <c r="V7" t="n">
-        <v>14.2</v>
+        <v>14.1</v>
       </c>
       <c r="W7" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="X7" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="Y7" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="Z7" t="n">
-        <v>18.5</v>
+        <v>18.7</v>
       </c>
       <c r="AA7" t="n">
-        <v>22.6</v>
+        <v>22.4</v>
       </c>
       <c r="AB7" t="n">
-        <v>102.9</v>
+        <v>103.8</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="AD7" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="AE7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AF7" t="n">
         <v>11</v>
       </c>
       <c r="AG7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AH7" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AI7" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AJ7" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="AK7" t="n">
         <v>8</v>
       </c>
       <c r="AL7" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AM7" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AN7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AO7" t="n">
         <v>3</v>
       </c>
       <c r="AP7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AQ7" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AR7" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AS7" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AT7" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AU7" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AV7" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AW7" t="n">
         <v>17</v>
       </c>
       <c r="AX7" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AY7" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AZ7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BA7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BB7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BC7" t="n">
         <v>9</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>12-4-2014-15</t>
+          <t>2014-12-04</t>
         </is>
       </c>
     </row>
@@ -1753,67 +1820,67 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E8" t="n">
         <v>15</v>
       </c>
       <c r="F8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G8" t="n">
-        <v>0.789</v>
+        <v>0.75</v>
       </c>
       <c r="H8" t="n">
         <v>48.8</v>
       </c>
       <c r="I8" t="n">
-        <v>41.5</v>
+        <v>41.3</v>
       </c>
       <c r="J8" t="n">
-        <v>86.90000000000001</v>
+        <v>86.5</v>
       </c>
       <c r="K8" t="n">
-        <v>0.477</v>
+        <v>0.478</v>
       </c>
       <c r="L8" t="n">
-        <v>9.5</v>
+        <v>9.4</v>
       </c>
       <c r="M8" t="n">
-        <v>27.7</v>
+        <v>27.4</v>
       </c>
       <c r="N8" t="n">
-        <v>0.342</v>
+        <v>0.344</v>
       </c>
       <c r="O8" t="n">
-        <v>18.3</v>
+        <v>18.2</v>
       </c>
       <c r="P8" t="n">
-        <v>23.9</v>
+        <v>23.7</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.764</v>
+        <v>0.767</v>
       </c>
       <c r="R8" t="n">
-        <v>11.5</v>
+        <v>11.4</v>
       </c>
       <c r="S8" t="n">
-        <v>31.2</v>
+        <v>30.8</v>
       </c>
       <c r="T8" t="n">
-        <v>42.6</v>
+        <v>42.2</v>
       </c>
       <c r="U8" t="n">
-        <v>24.7</v>
+        <v>24.4</v>
       </c>
       <c r="V8" t="n">
         <v>11.7</v>
       </c>
       <c r="W8" t="n">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="X8" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="Y8" t="n">
         <v>3.3</v>
@@ -1822,28 +1889,28 @@
         <v>20.9</v>
       </c>
       <c r="AA8" t="n">
-        <v>23.5</v>
+        <v>23.4</v>
       </c>
       <c r="AB8" t="n">
-        <v>110.7</v>
+        <v>110.2</v>
       </c>
       <c r="AC8" t="n">
-        <v>8.9</v>
+        <v>8.4</v>
       </c>
       <c r="AD8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AE8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF8" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AG8" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AH8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AI8" t="n">
         <v>1</v>
@@ -1855,52 +1922,52 @@
         <v>4</v>
       </c>
       <c r="AL8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AM8" t="n">
         <v>2</v>
       </c>
       <c r="AN8" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AO8" t="n">
         <v>11</v>
       </c>
       <c r="AP8" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AQ8" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AR8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AS8" t="n">
+        <v>20</v>
+      </c>
+      <c r="AT8" t="n">
         <v>18</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>13</v>
       </c>
       <c r="AU8" t="n">
         <v>5</v>
       </c>
       <c r="AV8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AW8" t="n">
         <v>14</v>
       </c>
       <c r="AX8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AY8" t="n">
         <v>2</v>
       </c>
       <c r="AZ8" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BB8" t="n">
         <v>1</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>12-4-2014-15</t>
+          <t>2014-12-04</t>
         </is>
       </c>
     </row>
@@ -2013,19 +2080,19 @@
         <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AE9" t="n">
+        <v>14</v>
+      </c>
+      <c r="AF9" t="n">
         <v>15</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>14</v>
       </c>
       <c r="AG9" t="n">
         <v>14</v>
       </c>
       <c r="AH9" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AI9" t="n">
         <v>10</v>
@@ -2040,7 +2107,7 @@
         <v>9</v>
       </c>
       <c r="AM9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AN9" t="n">
         <v>19</v>
@@ -2052,10 +2119,10 @@
         <v>7</v>
       </c>
       <c r="AQ9" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AR9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AS9" t="n">
         <v>9</v>
@@ -2064,10 +2131,10 @@
         <v>7</v>
       </c>
       <c r="AU9" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AV9" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AW9" t="n">
         <v>19</v>
@@ -2088,7 +2155,7 @@
         <v>5</v>
       </c>
       <c r="BC9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BD9" t="n">
         <v>10</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>12-4-2014-15</t>
+          <t>2014-12-04</t>
         </is>
       </c>
     </row>
@@ -2201,13 +2268,13 @@
         <v>29</v>
       </c>
       <c r="AF10" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AG10" t="n">
         <v>29</v>
       </c>
       <c r="AH10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AI10" t="n">
         <v>26</v>
@@ -2231,13 +2298,13 @@
         <v>26</v>
       </c>
       <c r="AP10" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ10" t="n">
         <v>29</v>
       </c>
       <c r="AR10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AS10" t="n">
         <v>13</v>
@@ -2252,10 +2319,10 @@
         <v>8</v>
       </c>
       <c r="AW10" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AX10" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AY10" t="n">
         <v>18</v>
@@ -2264,7 +2331,7 @@
         <v>8</v>
       </c>
       <c r="BA10" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BB10" t="n">
         <v>28</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>12-4-2014-15</t>
+          <t>2014-12-04</t>
         </is>
       </c>
     </row>
@@ -2299,64 +2366,64 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E11" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F11" t="n">
         <v>2</v>
       </c>
       <c r="G11" t="n">
-        <v>0.889</v>
+        <v>0.882</v>
       </c>
       <c r="H11" t="n">
         <v>48</v>
       </c>
       <c r="I11" t="n">
-        <v>40.3</v>
+        <v>39.9</v>
       </c>
       <c r="J11" t="n">
-        <v>83.2</v>
+        <v>82.2</v>
       </c>
       <c r="K11" t="n">
-        <v>0.484</v>
+        <v>0.485</v>
       </c>
       <c r="L11" t="n">
         <v>9.6</v>
       </c>
       <c r="M11" t="n">
-        <v>25.1</v>
+        <v>25.3</v>
       </c>
       <c r="N11" t="n">
-        <v>0.383</v>
+        <v>0.379</v>
       </c>
       <c r="O11" t="n">
-        <v>16.7</v>
+        <v>17.2</v>
       </c>
       <c r="P11" t="n">
-        <v>21.7</v>
+        <v>22</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.767</v>
+        <v>0.781</v>
       </c>
       <c r="R11" t="n">
-        <v>9.6</v>
+        <v>9.1</v>
       </c>
       <c r="S11" t="n">
-        <v>36.3</v>
+        <v>36.2</v>
       </c>
       <c r="T11" t="n">
-        <v>45.9</v>
+        <v>45.3</v>
       </c>
       <c r="U11" t="n">
-        <v>26</v>
+        <v>25.7</v>
       </c>
       <c r="V11" t="n">
-        <v>16.6</v>
+        <v>17.1</v>
       </c>
       <c r="W11" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="X11" t="n">
         <v>6.4</v>
@@ -2365,19 +2432,19 @@
         <v>3.5</v>
       </c>
       <c r="Z11" t="n">
-        <v>20.6</v>
+        <v>21.4</v>
       </c>
       <c r="AA11" t="n">
-        <v>19.3</v>
+        <v>19.6</v>
       </c>
       <c r="AB11" t="n">
-        <v>106.8</v>
+        <v>106.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>10.9</v>
+        <v>10</v>
       </c>
       <c r="AD11" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="AE11" t="n">
         <v>1</v>
@@ -2395,31 +2462,31 @@
         <v>3</v>
       </c>
       <c r="AJ11" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AK11" t="n">
         <v>1</v>
       </c>
       <c r="AL11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AM11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AN11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO11" t="n">
+        <v>19</v>
+      </c>
+      <c r="AP11" t="n">
         <v>21</v>
       </c>
-      <c r="AP11" t="n">
-        <v>24</v>
-      </c>
       <c r="AQ11" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="AR11" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AS11" t="n">
         <v>1</v>
@@ -2434,7 +2501,7 @@
         <v>28</v>
       </c>
       <c r="AW11" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AX11" t="n">
         <v>1</v>
@@ -2443,10 +2510,10 @@
         <v>4</v>
       </c>
       <c r="AZ11" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="BA11" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BB11" t="n">
         <v>3</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>12-4-2014-15</t>
+          <t>2014-12-04</t>
         </is>
       </c>
     </row>
@@ -2481,25 +2548,25 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F12" t="n">
         <v>4</v>
       </c>
       <c r="G12" t="n">
-        <v>0.765</v>
+        <v>0.778</v>
       </c>
       <c r="H12" t="n">
         <v>48</v>
       </c>
       <c r="I12" t="n">
-        <v>34.3</v>
+        <v>34.1</v>
       </c>
       <c r="J12" t="n">
-        <v>80.40000000000001</v>
+        <v>80</v>
       </c>
       <c r="K12" t="n">
         <v>0.426</v>
@@ -2508,76 +2575,76 @@
         <v>12.1</v>
       </c>
       <c r="M12" t="n">
-        <v>34.7</v>
+        <v>34.4</v>
       </c>
       <c r="N12" t="n">
-        <v>0.347</v>
+        <v>0.351</v>
       </c>
       <c r="O12" t="n">
-        <v>16.7</v>
+        <v>17.7</v>
       </c>
       <c r="P12" t="n">
-        <v>23.7</v>
+        <v>25.2</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.705</v>
+        <v>0.702</v>
       </c>
       <c r="R12" t="n">
-        <v>12.3</v>
+        <v>12.4</v>
       </c>
       <c r="S12" t="n">
-        <v>30.9</v>
+        <v>31.1</v>
       </c>
       <c r="T12" t="n">
-        <v>43.2</v>
+        <v>43.4</v>
       </c>
       <c r="U12" t="n">
-        <v>20.1</v>
+        <v>20.2</v>
       </c>
       <c r="V12" t="n">
-        <v>17.5</v>
+        <v>17.3</v>
       </c>
       <c r="W12" t="n">
-        <v>9.5</v>
+        <v>9.4</v>
       </c>
       <c r="X12" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="Y12" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="Z12" t="n">
-        <v>23.2</v>
+        <v>23.6</v>
       </c>
       <c r="AA12" t="n">
-        <v>20.5</v>
+        <v>21.1</v>
       </c>
       <c r="AB12" t="n">
-        <v>97.40000000000001</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="AC12" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="AD12" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="AE12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AF12" t="n">
         <v>3</v>
       </c>
       <c r="AG12" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AH12" t="n">
         <v>22</v>
       </c>
       <c r="AI12" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AJ12" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AK12" t="n">
         <v>27</v>
@@ -2592,10 +2659,10 @@
         <v>15</v>
       </c>
       <c r="AO12" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="AP12" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AQ12" t="n">
         <v>28</v>
@@ -2604,7 +2671,7 @@
         <v>3</v>
       </c>
       <c r="AS12" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AT12" t="n">
         <v>10</v>
@@ -2622,13 +2689,13 @@
         <v>7</v>
       </c>
       <c r="AY12" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AZ12" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="BA12" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="BB12" t="n">
         <v>21</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>12-4-2014-15</t>
+          <t>2014-12-04</t>
         </is>
       </c>
     </row>
@@ -2663,16 +2730,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E13" t="n">
         <v>7</v>
       </c>
       <c r="F13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G13" t="n">
-        <v>0.368</v>
+        <v>0.389</v>
       </c>
       <c r="H13" t="n">
         <v>48.3</v>
@@ -2681,43 +2748,43 @@
         <v>35.7</v>
       </c>
       <c r="J13" t="n">
-        <v>83.40000000000001</v>
+        <v>83</v>
       </c>
       <c r="K13" t="n">
-        <v>0.428</v>
+        <v>0.43</v>
       </c>
       <c r="L13" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="M13" t="n">
-        <v>21.4</v>
+        <v>21.6</v>
       </c>
       <c r="N13" t="n">
-        <v>0.334</v>
+        <v>0.337</v>
       </c>
       <c r="O13" t="n">
-        <v>14.6</v>
+        <v>15.1</v>
       </c>
       <c r="P13" t="n">
-        <v>20.3</v>
+        <v>20.9</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.719</v>
+        <v>0.721</v>
       </c>
       <c r="R13" t="n">
-        <v>12.2</v>
+        <v>12.3</v>
       </c>
       <c r="S13" t="n">
-        <v>34.1</v>
+        <v>33.8</v>
       </c>
       <c r="T13" t="n">
-        <v>46.3</v>
+        <v>46.1</v>
       </c>
       <c r="U13" t="n">
         <v>19</v>
       </c>
       <c r="V13" t="n">
-        <v>15.1</v>
+        <v>15</v>
       </c>
       <c r="W13" t="n">
         <v>4.9</v>
@@ -2732,28 +2799,28 @@
         <v>20.4</v>
       </c>
       <c r="AA13" t="n">
-        <v>20.9</v>
+        <v>21.2</v>
       </c>
       <c r="AB13" t="n">
-        <v>93.09999999999999</v>
+        <v>93.7</v>
       </c>
       <c r="AC13" t="n">
-        <v>-2.9</v>
+        <v>-2.7</v>
       </c>
       <c r="AD13" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="AE13" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AF13" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AG13" t="n">
         <v>20</v>
       </c>
       <c r="AH13" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AI13" t="n">
         <v>25</v>
@@ -2765,25 +2832,25 @@
         <v>25</v>
       </c>
       <c r="AL13" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AM13" t="n">
         <v>16</v>
       </c>
       <c r="AN13" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AO13" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AP13" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AQ13" t="n">
         <v>26</v>
       </c>
       <c r="AR13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AS13" t="n">
         <v>4</v>
@@ -2807,13 +2874,13 @@
         <v>20</v>
       </c>
       <c r="AZ13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BA13" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BB13" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BC13" t="n">
         <v>21</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>12-4-2014-15</t>
+          <t>2014-12-04</t>
         </is>
       </c>
     </row>
@@ -2923,13 +2990,13 @@
         <v>7.2</v>
       </c>
       <c r="AD14" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AE14" t="n">
+        <v>7</v>
+      </c>
+      <c r="AF14" t="n">
         <v>6</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>7</v>
       </c>
       <c r="AG14" t="n">
         <v>7</v>
@@ -2938,7 +3005,7 @@
         <v>22</v>
       </c>
       <c r="AI14" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AJ14" t="n">
         <v>27</v>
@@ -2953,16 +3020,16 @@
         <v>3</v>
       </c>
       <c r="AN14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AO14" t="n">
         <v>10</v>
       </c>
       <c r="AP14" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ14" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AR14" t="n">
         <v>30</v>
@@ -2974,7 +3041,7 @@
         <v>28</v>
       </c>
       <c r="AU14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AV14" t="n">
         <v>6</v>
@@ -2989,10 +3056,10 @@
         <v>3</v>
       </c>
       <c r="AZ14" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BA14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BB14" t="n">
         <v>4</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>12-4-2014-15</t>
+          <t>2014-12-04</t>
         </is>
       </c>
     </row>
@@ -3027,64 +3094,64 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E15" t="n">
         <v>5</v>
       </c>
       <c r="F15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G15" t="n">
-        <v>0.278</v>
+        <v>0.263</v>
       </c>
       <c r="H15" t="n">
-        <v>48.6</v>
+        <v>48.5</v>
       </c>
       <c r="I15" t="n">
-        <v>38.9</v>
+        <v>38.4</v>
       </c>
       <c r="J15" t="n">
-        <v>86.40000000000001</v>
+        <v>86</v>
       </c>
       <c r="K15" t="n">
-        <v>0.451</v>
+        <v>0.446</v>
       </c>
       <c r="L15" t="n">
-        <v>6.3</v>
+        <v>6.1</v>
       </c>
       <c r="M15" t="n">
-        <v>18.6</v>
+        <v>18.2</v>
       </c>
       <c r="N15" t="n">
-        <v>0.337</v>
+        <v>0.336</v>
       </c>
       <c r="O15" t="n">
-        <v>20.3</v>
+        <v>20.8</v>
       </c>
       <c r="P15" t="n">
-        <v>27.2</v>
+        <v>27.8</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.746</v>
+        <v>0.75</v>
       </c>
       <c r="R15" t="n">
-        <v>12.6</v>
+        <v>12.5</v>
       </c>
       <c r="S15" t="n">
-        <v>30</v>
+        <v>29.7</v>
       </c>
       <c r="T15" t="n">
-        <v>42.6</v>
+        <v>42.3</v>
       </c>
       <c r="U15" t="n">
-        <v>20.4</v>
+        <v>20.2</v>
       </c>
       <c r="V15" t="n">
         <v>12.6</v>
       </c>
       <c r="W15" t="n">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="X15" t="n">
         <v>4.4</v>
@@ -3093,40 +3160,40 @@
         <v>3.9</v>
       </c>
       <c r="Z15" t="n">
-        <v>22.5</v>
+        <v>23</v>
       </c>
       <c r="AA15" t="n">
-        <v>22.2</v>
+        <v>22.6</v>
       </c>
       <c r="AB15" t="n">
-        <v>104.4</v>
+        <v>103.7</v>
       </c>
       <c r="AC15" t="n">
-        <v>-6.8</v>
+        <v>-7.4</v>
       </c>
       <c r="AD15" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="AE15" t="n">
         <v>22</v>
       </c>
       <c r="AF15" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AG15" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AH15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AI15" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="AJ15" t="n">
         <v>3</v>
       </c>
       <c r="AK15" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="AL15" t="n">
         <v>25</v>
@@ -3135,49 +3202,49 @@
         <v>24</v>
       </c>
       <c r="AN15" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AO15" t="n">
         <v>5</v>
       </c>
       <c r="AP15" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AQ15" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AR15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AS15" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AT15" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AU15" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AV15" t="n">
         <v>5</v>
       </c>
       <c r="AW15" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AX15" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AY15" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AZ15" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="BA15" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BB15" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="BC15" t="n">
         <v>27</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>12-4-2014-15</t>
+          <t>2014-12-04</t>
         </is>
       </c>
     </row>
@@ -3287,10 +3354,10 @@
         <v>7.1</v>
       </c>
       <c r="AD16" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AE16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF16" t="n">
         <v>2</v>
@@ -3323,10 +3390,10 @@
         <v>8</v>
       </c>
       <c r="AP16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AR16" t="n">
         <v>17</v>
@@ -3335,7 +3402,7 @@
         <v>17</v>
       </c>
       <c r="AT16" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AU16" t="n">
         <v>11</v>
@@ -3350,13 +3417,13 @@
         <v>27</v>
       </c>
       <c r="AY16" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ16" t="n">
         <v>6</v>
       </c>
       <c r="BA16" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BB16" t="n">
         <v>15</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>12-4-2014-15</t>
+          <t>2014-12-04</t>
         </is>
       </c>
     </row>
@@ -3469,13 +3536,13 @@
         <v>-1.8</v>
       </c>
       <c r="AD17" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AE17" t="n">
+        <v>14</v>
+      </c>
+      <c r="AF17" t="n">
         <v>15</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>14</v>
       </c>
       <c r="AG17" t="n">
         <v>14</v>
@@ -3484,7 +3551,7 @@
         <v>22</v>
       </c>
       <c r="AI17" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AJ17" t="n">
         <v>30</v>
@@ -3499,7 +3566,7 @@
         <v>12</v>
       </c>
       <c r="AN17" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AO17" t="n">
         <v>9</v>
@@ -3508,7 +3575,7 @@
         <v>8</v>
       </c>
       <c r="AQ17" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AR17" t="n">
         <v>29</v>
@@ -3529,13 +3596,13 @@
         <v>7</v>
       </c>
       <c r="AX17" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AY17" t="n">
         <v>10</v>
       </c>
       <c r="AZ17" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA17" t="n">
         <v>14</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>12-4-2014-15</t>
+          <t>2014-12-04</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3718,7 @@
         <v>-1.4</v>
       </c>
       <c r="AD18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE18" t="n">
         <v>13</v>
@@ -3666,13 +3733,13 @@
         <v>2</v>
       </c>
       <c r="AI18" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AJ18" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AK18" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AL18" t="n">
         <v>24</v>
@@ -3681,16 +3748,16 @@
         <v>23</v>
       </c>
       <c r="AN18" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AO18" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AP18" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ18" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AR18" t="n">
         <v>9</v>
@@ -3699,7 +3766,7 @@
         <v>21</v>
       </c>
       <c r="AT18" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AU18" t="n">
         <v>9</v>
@@ -3711,16 +3778,16 @@
         <v>2</v>
       </c>
       <c r="AX18" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AY18" t="n">
         <v>21</v>
       </c>
       <c r="AZ18" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BA18" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BB18" t="n">
         <v>20</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>12-4-2014-15</t>
+          <t>2014-12-04</t>
         </is>
       </c>
     </row>
@@ -3833,7 +3900,7 @@
         <v>-10.2</v>
       </c>
       <c r="AD19" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AE19" t="n">
         <v>26</v>
@@ -3845,10 +3912,10 @@
         <v>26</v>
       </c>
       <c r="AH19" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AI19" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AJ19" t="n">
         <v>8</v>
@@ -3872,10 +3939,10 @@
         <v>6</v>
       </c>
       <c r="AQ19" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AR19" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AS19" t="n">
         <v>28</v>
@@ -3884,7 +3951,7 @@
         <v>26</v>
       </c>
       <c r="AU19" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AV19" t="n">
         <v>23</v>
@@ -3896,7 +3963,7 @@
         <v>26</v>
       </c>
       <c r="AY19" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AZ19" t="n">
         <v>19</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>12-4-2014-15</t>
+          <t>2014-12-04</t>
         </is>
       </c>
     </row>
@@ -3940,157 +4007,157 @@
         <v>16</v>
       </c>
       <c r="E20" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F20" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G20" t="n">
-        <v>0.438</v>
+        <v>0.5</v>
       </c>
       <c r="H20" t="n">
         <v>48</v>
       </c>
       <c r="I20" t="n">
-        <v>38.3</v>
+        <v>38.5</v>
       </c>
       <c r="J20" t="n">
-        <v>85.09999999999999</v>
+        <v>85.8</v>
       </c>
       <c r="K20" t="n">
-        <v>0.45</v>
+        <v>0.449</v>
       </c>
       <c r="L20" t="n">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="M20" t="n">
-        <v>19.6</v>
+        <v>19.8</v>
       </c>
       <c r="N20" t="n">
-        <v>0.338</v>
+        <v>0.339</v>
       </c>
       <c r="O20" t="n">
-        <v>17.1</v>
+        <v>17.5</v>
       </c>
       <c r="P20" t="n">
-        <v>22.9</v>
+        <v>24.1</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.744</v>
+        <v>0.727</v>
       </c>
       <c r="R20" t="n">
-        <v>11.4</v>
+        <v>12.4</v>
       </c>
       <c r="S20" t="n">
-        <v>30.4</v>
+        <v>30.3</v>
       </c>
       <c r="T20" t="n">
-        <v>41.8</v>
+        <v>42.7</v>
       </c>
       <c r="U20" t="n">
-        <v>21.6</v>
+        <v>21.4</v>
       </c>
       <c r="V20" t="n">
-        <v>11.8</v>
+        <v>11.3</v>
       </c>
       <c r="W20" t="n">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="X20" t="n">
-        <v>5.5</v>
+        <v>6.3</v>
       </c>
       <c r="Y20" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="Z20" t="n">
-        <v>21.6</v>
+        <v>21.8</v>
       </c>
       <c r="AA20" t="n">
-        <v>19</v>
+        <v>20.1</v>
       </c>
       <c r="AB20" t="n">
-        <v>100.2</v>
+        <v>101.2</v>
       </c>
       <c r="AC20" t="n">
-        <v>-0.7</v>
+        <v>2.1</v>
       </c>
       <c r="AD20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AE20" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AF20" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG20" t="n">
         <v>14</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>19</v>
       </c>
       <c r="AH20" t="n">
         <v>22</v>
       </c>
       <c r="AI20" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AJ20" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AK20" t="n">
+        <v>20</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>22</v>
+      </c>
+      <c r="AM20" t="n">
         <v>21</v>
       </c>
-      <c r="AL20" t="n">
-        <v>23</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>22</v>
-      </c>
       <c r="AN20" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AO20" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AP20" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AQ20" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="AR20" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="AS20" t="n">
         <v>22</v>
       </c>
       <c r="AT20" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="AU20" t="n">
         <v>14</v>
       </c>
       <c r="AV20" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AW20" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AX20" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AY20" t="n">
+        <v>26</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>18</v>
+      </c>
+      <c r="BA20" t="n">
         <v>24</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>17</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>29</v>
       </c>
       <c r="BB20" t="n">
         <v>14</v>
       </c>
       <c r="BC20" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="BD20" t="n">
         <v>10</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>12-4-2014-15</t>
+          <t>2014-12-04</t>
         </is>
       </c>
     </row>
@@ -4119,112 +4186,112 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E21" t="n">
         <v>4</v>
       </c>
       <c r="F21" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G21" t="n">
-        <v>0.2</v>
+        <v>0.211</v>
       </c>
       <c r="H21" t="n">
         <v>48.3</v>
       </c>
       <c r="I21" t="n">
-        <v>36.2</v>
+        <v>36.1</v>
       </c>
       <c r="J21" t="n">
-        <v>81</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="K21" t="n">
-        <v>0.447</v>
+        <v>0.448</v>
       </c>
       <c r="L21" t="n">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="M21" t="n">
-        <v>19.8</v>
+        <v>19.5</v>
       </c>
       <c r="N21" t="n">
-        <v>0.366</v>
+        <v>0.37</v>
       </c>
       <c r="O21" t="n">
-        <v>13.5</v>
+        <v>13.9</v>
       </c>
       <c r="P21" t="n">
-        <v>17.5</v>
+        <v>18.1</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.774</v>
+        <v>0.773</v>
       </c>
       <c r="R21" t="n">
-        <v>11.4</v>
+        <v>11.1</v>
       </c>
       <c r="S21" t="n">
-        <v>28.6</v>
+        <v>28.5</v>
       </c>
       <c r="T21" t="n">
-        <v>40</v>
+        <v>39.6</v>
       </c>
       <c r="U21" t="n">
-        <v>21.1</v>
+        <v>20.8</v>
       </c>
       <c r="V21" t="n">
-        <v>15.4</v>
+        <v>15</v>
       </c>
       <c r="W21" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="X21" t="n">
         <v>3.5</v>
       </c>
       <c r="Y21" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="Z21" t="n">
         <v>24.1</v>
       </c>
       <c r="AA21" t="n">
-        <v>19.8</v>
+        <v>20</v>
       </c>
       <c r="AB21" t="n">
-        <v>93.09999999999999</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="AC21" t="n">
-        <v>-5.6</v>
+        <v>-5.7</v>
       </c>
       <c r="AD21" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AE21" t="n">
         <v>26</v>
       </c>
       <c r="AF21" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AG21" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AH21" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AI21" t="n">
         <v>21</v>
       </c>
       <c r="AJ21" t="n">
+        <v>23</v>
+      </c>
+      <c r="AK21" t="n">
         <v>21</v>
       </c>
-      <c r="AK21" t="n">
-        <v>23</v>
-      </c>
       <c r="AL21" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AM21" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AN21" t="n">
         <v>8</v>
@@ -4239,7 +4306,7 @@
         <v>10</v>
       </c>
       <c r="AR21" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AS21" t="n">
         <v>30</v>
@@ -4248,10 +4315,10 @@
         <v>27</v>
       </c>
       <c r="AU21" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AV21" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AW21" t="n">
         <v>23</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>12-4-2014-15</t>
+          <t>2014-12-04</t>
         </is>
       </c>
     </row>
@@ -4379,7 +4446,7 @@
         <v>-2.6</v>
       </c>
       <c r="AD22" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AE22" t="n">
         <v>22</v>
@@ -4391,10 +4458,10 @@
         <v>23</v>
       </c>
       <c r="AH22" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AI22" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AJ22" t="n">
         <v>22</v>
@@ -4415,13 +4482,13 @@
         <v>25</v>
       </c>
       <c r="AP22" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AQ22" t="n">
         <v>25</v>
       </c>
       <c r="AR22" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AS22" t="n">
         <v>7</v>
@@ -4436,10 +4503,10 @@
         <v>24</v>
       </c>
       <c r="AW22" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AX22" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AY22" t="n">
         <v>22</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>12-4-2014-15</t>
+          <t>2014-12-04</t>
         </is>
       </c>
     </row>
@@ -4483,97 +4550,97 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E23" t="n">
         <v>7</v>
       </c>
       <c r="F23" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G23" t="n">
-        <v>0.35</v>
+        <v>0.333</v>
       </c>
       <c r="H23" t="n">
-        <v>48.3</v>
+        <v>48.2</v>
       </c>
       <c r="I23" t="n">
-        <v>36.7</v>
+        <v>36.4</v>
       </c>
       <c r="J23" t="n">
-        <v>80.40000000000001</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="K23" t="n">
-        <v>0.456</v>
+        <v>0.452</v>
       </c>
       <c r="L23" t="n">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="M23" t="n">
-        <v>18.1</v>
+        <v>17.7</v>
       </c>
       <c r="N23" t="n">
         <v>0.371</v>
       </c>
       <c r="O23" t="n">
-        <v>14.8</v>
+        <v>14.9</v>
       </c>
       <c r="P23" t="n">
         <v>20.7</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.717</v>
+        <v>0.719</v>
       </c>
       <c r="R23" t="n">
-        <v>8.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="S23" t="n">
-        <v>32.6</v>
+        <v>32.9</v>
       </c>
       <c r="T23" t="n">
-        <v>41.5</v>
+        <v>42.1</v>
       </c>
       <c r="U23" t="n">
-        <v>19.8</v>
+        <v>19.6</v>
       </c>
       <c r="V23" t="n">
-        <v>15.9</v>
+        <v>16</v>
       </c>
       <c r="W23" t="n">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="X23" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="Y23" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="Z23" t="n">
-        <v>21</v>
+        <v>21.2</v>
       </c>
       <c r="AA23" t="n">
-        <v>20.2</v>
+        <v>20</v>
       </c>
       <c r="AB23" t="n">
-        <v>94.8</v>
+        <v>94.3</v>
       </c>
       <c r="AC23" t="n">
-        <v>-5.8</v>
+        <v>-6.3</v>
       </c>
       <c r="AD23" t="n">
         <v>1</v>
       </c>
       <c r="AE23" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AF23" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AG23" t="n">
         <v>21</v>
       </c>
       <c r="AH23" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AI23" t="n">
         <v>20</v>
@@ -4582,34 +4649,34 @@
         <v>24</v>
       </c>
       <c r="AK23" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AL23" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AM23" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AN23" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AO23" t="n">
+        <v>29</v>
+      </c>
+      <c r="AP23" t="n">
         <v>28</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>27</v>
       </c>
       <c r="AQ23" t="n">
         <v>27</v>
       </c>
       <c r="AR23" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AS23" t="n">
         <v>8</v>
       </c>
       <c r="AT23" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AU23" t="n">
         <v>26</v>
@@ -4618,25 +4685,25 @@
         <v>25</v>
       </c>
       <c r="AW23" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AX23" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AY23" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="AZ23" t="n">
         <v>15</v>
       </c>
       <c r="BA23" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="BB23" t="n">
         <v>24</v>
       </c>
       <c r="BC23" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BD23" t="n">
         <v>10</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>12-4-2014-15</t>
+          <t>2014-12-04</t>
         </is>
       </c>
     </row>
@@ -4743,7 +4810,7 @@
         <v>-13.2</v>
       </c>
       <c r="AD24" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AE24" t="n">
         <v>30</v>
@@ -4761,7 +4828,7 @@
         <v>30</v>
       </c>
       <c r="AJ24" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AK24" t="n">
         <v>29</v>
@@ -4776,16 +4843,16 @@
         <v>30</v>
       </c>
       <c r="AO24" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AP24" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ24" t="n">
         <v>30</v>
       </c>
       <c r="AR24" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AS24" t="n">
         <v>27</v>
@@ -4794,7 +4861,7 @@
         <v>25</v>
       </c>
       <c r="AU24" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AV24" t="n">
         <v>30</v>
@@ -4809,10 +4876,10 @@
         <v>27</v>
       </c>
       <c r="AZ24" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BA24" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BB24" t="n">
         <v>30</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>12-4-2014-15</t>
+          <t>2014-12-04</t>
         </is>
       </c>
     </row>
@@ -4934,28 +5001,28 @@
         <v>13</v>
       </c>
       <c r="AG25" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AH25" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AI25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AJ25" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AK25" t="n">
         <v>15</v>
       </c>
       <c r="AL25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AM25" t="n">
         <v>4</v>
       </c>
       <c r="AN25" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AO25" t="n">
         <v>13</v>
@@ -4967,22 +5034,22 @@
         <v>1</v>
       </c>
       <c r="AR25" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AS25" t="n">
         <v>12</v>
       </c>
       <c r="AT25" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AU25" t="n">
         <v>20</v>
       </c>
       <c r="AV25" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AW25" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AX25" t="n">
         <v>23</v>
@@ -4991,7 +5058,7 @@
         <v>8</v>
       </c>
       <c r="AZ25" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BA25" t="n">
         <v>10</v>
@@ -5000,7 +5067,7 @@
         <v>6</v>
       </c>
       <c r="BC25" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BD25" t="n">
         <v>10</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>12-4-2014-15</t>
+          <t>2014-12-04</t>
         </is>
       </c>
     </row>
@@ -5029,121 +5096,121 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E26" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F26" t="n">
         <v>4</v>
       </c>
       <c r="G26" t="n">
-        <v>0.789</v>
+        <v>0.778</v>
       </c>
       <c r="H26" t="n">
         <v>48</v>
       </c>
       <c r="I26" t="n">
-        <v>38.8</v>
+        <v>39.1</v>
       </c>
       <c r="J26" t="n">
-        <v>85.59999999999999</v>
+        <v>85.8</v>
       </c>
       <c r="K26" t="n">
-        <v>0.453</v>
+        <v>0.456</v>
       </c>
       <c r="L26" t="n">
-        <v>9.4</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="M26" t="n">
-        <v>25.7</v>
+        <v>26</v>
       </c>
       <c r="N26" t="n">
-        <v>0.366</v>
+        <v>0.374</v>
       </c>
       <c r="O26" t="n">
-        <v>16.4</v>
+        <v>16.3</v>
       </c>
       <c r="P26" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="Q26" t="n">
         <v>0.788</v>
       </c>
       <c r="R26" t="n">
-        <v>11.5</v>
+        <v>11.9</v>
       </c>
       <c r="S26" t="n">
-        <v>35.9</v>
+        <v>35.6</v>
       </c>
       <c r="T26" t="n">
-        <v>47.5</v>
+        <v>47.4</v>
       </c>
       <c r="U26" t="n">
-        <v>23.9</v>
+        <v>24.1</v>
       </c>
       <c r="V26" t="n">
-        <v>13.9</v>
+        <v>14.1</v>
       </c>
       <c r="W26" t="n">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="X26" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="Y26" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="Z26" t="n">
-        <v>19.5</v>
+        <v>19.7</v>
       </c>
       <c r="AA26" t="n">
-        <v>20</v>
+        <v>20.1</v>
       </c>
       <c r="AB26" t="n">
-        <v>103.4</v>
+        <v>104.3</v>
       </c>
       <c r="AC26" t="n">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="AD26" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="AE26" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AF26" t="n">
         <v>3</v>
       </c>
       <c r="AG26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AH26" t="n">
         <v>22</v>
       </c>
       <c r="AI26" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AJ26" t="n">
+        <v>6</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>14</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AN26" t="n">
         <v>5</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>16</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>6</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>5</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>9</v>
       </c>
       <c r="AO26" t="n">
         <v>22</v>
       </c>
       <c r="AP26" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ26" t="n">
         <v>5</v>
@@ -5158,13 +5225,13 @@
         <v>1</v>
       </c>
       <c r="AU26" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AV26" t="n">
         <v>9</v>
       </c>
       <c r="AW26" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AX26" t="n">
         <v>5</v>
@@ -5179,7 +5246,7 @@
         <v>25</v>
       </c>
       <c r="BB26" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="BC26" t="n">
         <v>4</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>12-4-2014-15</t>
+          <t>2014-12-04</t>
         </is>
       </c>
     </row>
@@ -5289,13 +5356,13 @@
         <v>0.1</v>
       </c>
       <c r="AD27" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AE27" t="n">
+        <v>14</v>
+      </c>
+      <c r="AF27" t="n">
         <v>15</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>14</v>
       </c>
       <c r="AG27" t="n">
         <v>14</v>
@@ -5331,13 +5398,13 @@
         <v>3</v>
       </c>
       <c r="AR27" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AS27" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AT27" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AU27" t="n">
         <v>27</v>
@@ -5346,7 +5413,7 @@
         <v>26</v>
       </c>
       <c r="AW27" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AX27" t="n">
         <v>24</v>
@@ -5355,7 +5422,7 @@
         <v>30</v>
       </c>
       <c r="AZ27" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BA27" t="n">
         <v>1</v>
@@ -5364,7 +5431,7 @@
         <v>13</v>
       </c>
       <c r="BC27" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BD27" t="n">
         <v>10</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>12-4-2014-15</t>
+          <t>2014-12-04</t>
         </is>
       </c>
     </row>
@@ -5393,16 +5460,16 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E28" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F28" t="n">
         <v>5</v>
       </c>
       <c r="G28" t="n">
-        <v>0.706</v>
+        <v>0.722</v>
       </c>
       <c r="H28" t="n">
         <v>48.3</v>
@@ -5411,88 +5478,88 @@
         <v>37.1</v>
       </c>
       <c r="J28" t="n">
-        <v>82.09999999999999</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="K28" t="n">
-        <v>0.451</v>
+        <v>0.455</v>
       </c>
       <c r="L28" t="n">
-        <v>7.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="M28" t="n">
-        <v>22.2</v>
+        <v>22.6</v>
       </c>
       <c r="N28" t="n">
-        <v>0.354</v>
+        <v>0.365</v>
       </c>
       <c r="O28" t="n">
-        <v>17.5</v>
+        <v>17.3</v>
       </c>
       <c r="P28" t="n">
-        <v>22.4</v>
+        <v>22</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.784</v>
+        <v>0.785</v>
       </c>
       <c r="R28" t="n">
         <v>9.6</v>
       </c>
       <c r="S28" t="n">
-        <v>35.6</v>
+        <v>35.3</v>
       </c>
       <c r="T28" t="n">
-        <v>45.3</v>
+        <v>44.9</v>
       </c>
       <c r="U28" t="n">
-        <v>24</v>
+        <v>23.9</v>
       </c>
       <c r="V28" t="n">
-        <v>14</v>
+        <v>14.4</v>
       </c>
       <c r="W28" t="n">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="X28" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="Y28" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="Z28" t="n">
-        <v>18.9</v>
+        <v>19</v>
       </c>
       <c r="AA28" t="n">
         <v>19.2</v>
       </c>
       <c r="AB28" t="n">
-        <v>99.5</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="AC28" t="n">
-        <v>6.7</v>
+        <v>6.4</v>
       </c>
       <c r="AD28" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="AE28" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AF28" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG28" t="n">
         <v>7</v>
       </c>
-      <c r="AG28" t="n">
-        <v>8</v>
-      </c>
       <c r="AH28" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AI28" t="n">
         <v>17</v>
       </c>
       <c r="AJ28" t="n">
+        <v>18</v>
+      </c>
+      <c r="AK28" t="n">
         <v>16</v>
-      </c>
-      <c r="AK28" t="n">
-        <v>18</v>
       </c>
       <c r="AL28" t="n">
         <v>11</v>
@@ -5501,13 +5568,13 @@
         <v>14</v>
       </c>
       <c r="AN28" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AO28" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="AP28" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AQ28" t="n">
         <v>7</v>
@@ -5519,28 +5586,28 @@
         <v>3</v>
       </c>
       <c r="AT28" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AU28" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AV28" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AW28" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AX28" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AY28" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ28" t="n">
         <v>4</v>
       </c>
       <c r="BA28" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BB28" t="n">
         <v>16</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>12-4-2014-15</t>
+          <t>2014-12-04</t>
         </is>
       </c>
     </row>
@@ -5656,7 +5723,7 @@
         <v>4</v>
       </c>
       <c r="AE29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF29" t="n">
         <v>3</v>
@@ -5665,7 +5732,7 @@
         <v>3</v>
       </c>
       <c r="AH29" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AI29" t="n">
         <v>6</v>
@@ -5683,7 +5750,7 @@
         <v>10</v>
       </c>
       <c r="AN29" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AO29" t="n">
         <v>2</v>
@@ -5701,16 +5768,16 @@
         <v>23</v>
       </c>
       <c r="AT29" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AU29" t="n">
         <v>25</v>
       </c>
       <c r="AV29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW29" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AX29" t="n">
         <v>15</v>
@@ -5719,16 +5786,16 @@
         <v>19</v>
       </c>
       <c r="AZ29" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BA29" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BB29" t="n">
         <v>2</v>
       </c>
       <c r="BC29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BD29" t="n">
         <v>10</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>12-4-2014-15</t>
+          <t>2014-12-04</t>
         </is>
       </c>
     </row>
@@ -5841,10 +5908,10 @@
         <v>22</v>
       </c>
       <c r="AF30" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AG30" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AH30" t="n">
         <v>22</v>
@@ -5868,22 +5935,22 @@
         <v>25</v>
       </c>
       <c r="AO30" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AP30" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AQ30" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AR30" t="n">
         <v>15</v>
       </c>
       <c r="AS30" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AT30" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AU30" t="n">
         <v>18</v>
@@ -5898,7 +5965,7 @@
         <v>11</v>
       </c>
       <c r="AY30" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AZ30" t="n">
         <v>1</v>
@@ -5910,7 +5977,7 @@
         <v>22</v>
       </c>
       <c r="BC30" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BD30" t="n">
         <v>10</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>12-4-2014-15</t>
+          <t>2014-12-04</t>
         </is>
       </c>
     </row>
@@ -6017,25 +6084,25 @@
         <v>3</v>
       </c>
       <c r="AD31" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AE31" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF31" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AG31" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AH31" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AI31" t="n">
         <v>12</v>
       </c>
       <c r="AJ31" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AK31" t="n">
         <v>5</v>
@@ -6050,13 +6117,13 @@
         <v>3</v>
       </c>
       <c r="AO31" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AP31" t="n">
         <v>17</v>
       </c>
       <c r="AQ31" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AR31" t="n">
         <v>19</v>
@@ -6071,19 +6138,19 @@
         <v>4</v>
       </c>
       <c r="AV31" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AW31" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AX31" t="n">
         <v>16</v>
       </c>
       <c r="AY31" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AZ31" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BA31" t="n">
         <v>12</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>12-4-2014-15</t>
+          <t>2014-12-04</t>
         </is>
       </c>
     </row>
